--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0269364-B8A4-4FB2-9C97-E4DB89EC4E33}"/>
+  <xr:revisionPtr revIDLastSave="565" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF99CF4A-C45E-4AE5-A8A4-3EEF35653D76}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="287">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -478,9 +478,6 @@
     <t>Escuela de Lenguaje El Trigal</t>
   </si>
   <si>
-    <t>Escuela Julio Tejedor Zúñiga</t>
-  </si>
-  <si>
     <t>Colegio Renacer</t>
   </si>
   <si>
@@ -688,9 +685,6 @@
     <t>Liceo Polivalente Rigoberto Fontt</t>
   </si>
   <si>
-    <t>Colegio Chillán</t>
-  </si>
-  <si>
     <t>Colegio La Merced</t>
   </si>
   <si>
@@ -857,9 +851,6 @@
   </si>
   <si>
     <t>Liceo Salvador González</t>
-  </si>
-  <si>
-    <t>Colegio Cumbres de Llay Llay</t>
   </si>
   <si>
     <t>Colegio Genesaret</t>
@@ -1697,10 +1688,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9">
-        <v>1.0089999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1714,10 +1705,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10">
-        <v>1.0940000000000001</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1748,10 +1739,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12">
-        <v>1.452</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1782,10 +1773,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14">
-        <v>1.0649999999999999</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1799,10 +1790,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15">
-        <v>1.1000000000000001</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1816,10 +1807,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E16">
-        <v>0.98399999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1884,10 +1875,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>1.024</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1935,10 +1926,10 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E23">
-        <v>1.079</v>
+        <v>1.105</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1986,10 +1977,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26">
-        <v>1.012</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2003,10 +1994,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>0.96299999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2020,10 +2011,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E28">
-        <v>1.0209999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2071,10 +2062,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E31">
-        <v>1.0720000000000001</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2088,10 +2079,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E32">
-        <v>1.0609999999999999</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2105,10 +2096,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E33">
-        <v>1.036</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2139,10 +2130,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E35">
-        <v>0.995</v>
+        <v>0.99099999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2156,10 +2147,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E36">
-        <v>1.024</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2190,10 +2181,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E38">
-        <v>1.0880000000000001</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2223,12 +2214,12 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C336"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2261,7 +2252,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2316,7 +2307,7 @@
         <v>46006</v>
       </c>
       <c r="C8" s="6">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2371,7 +2362,7 @@
         <v>46010</v>
       </c>
       <c r="C13" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2445,10 +2436,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46021</v>
+        <v>46275</v>
       </c>
       <c r="C20" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2456,10 +2447,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="8">
-        <v>46080</v>
+        <v>46021</v>
       </c>
       <c r="C21" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2467,10 +2458,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="5">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="C22" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2478,10 +2469,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="8">
-        <v>46254</v>
+        <v>46087</v>
       </c>
       <c r="C23" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2489,7 +2480,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46022</v>
+        <v>46273</v>
       </c>
       <c r="C24" s="6">
         <v>3</v>
@@ -2500,7 +2491,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46161</v>
+        <v>46254</v>
       </c>
       <c r="C25" s="9">
         <v>1</v>
@@ -2511,7 +2502,7 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46086</v>
+        <v>46022</v>
       </c>
       <c r="C26" s="6">
         <v>3</v>
@@ -2522,10 +2513,10 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46211</v>
+        <v>46161</v>
       </c>
       <c r="C27" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2533,10 +2524,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46020</v>
+        <v>46086</v>
       </c>
       <c r="C28" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2544,10 +2535,10 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46076</v>
+        <v>46211</v>
       </c>
       <c r="C29" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2555,10 +2546,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46136</v>
+        <v>46020</v>
       </c>
       <c r="C30" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2566,10 +2557,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="C31" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2577,10 +2568,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46176</v>
+        <v>46136</v>
       </c>
       <c r="C32" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2588,10 +2579,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46182</v>
+        <v>46078</v>
       </c>
       <c r="C33" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2599,10 +2590,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46262</v>
+        <v>46176</v>
       </c>
       <c r="C34" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2610,10 +2601,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46098</v>
+        <v>46182</v>
       </c>
       <c r="C35" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2621,10 +2612,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46181</v>
+        <v>46262</v>
       </c>
       <c r="C36" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2632,10 +2623,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C37" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2643,7 +2634,7 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46160</v>
+        <v>46181</v>
       </c>
       <c r="C38" s="6">
         <v>3</v>
@@ -2654,10 +2645,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46167</v>
+        <v>46084</v>
       </c>
       <c r="C39" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2665,10 +2656,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46099</v>
+        <v>46160</v>
       </c>
       <c r="C40" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2676,10 +2667,10 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46128</v>
+        <v>46167</v>
       </c>
       <c r="C41" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2687,10 +2678,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46141</v>
+        <v>46099</v>
       </c>
       <c r="C42" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2698,7 +2689,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="C43" s="9">
         <v>1</v>
@@ -2709,10 +2700,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46246</v>
+        <v>46141</v>
       </c>
       <c r="C44" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2720,10 +2711,10 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C45" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2731,7 +2722,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="C46" s="6">
         <v>2</v>
@@ -2742,10 +2733,10 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46225</v>
+        <v>46127</v>
       </c>
       <c r="C47" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2753,10 +2744,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="C48" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2764,10 +2755,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46091</v>
+        <v>46212</v>
       </c>
       <c r="C49" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2775,10 +2766,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C50" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2786,7 +2777,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C51" s="9">
         <v>1</v>
@@ -2797,7 +2788,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2808,7 +2799,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2819,7 +2810,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46184</v>
+        <v>46276</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2830,10 +2821,10 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C55" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2841,10 +2832,10 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46210</v>
+        <v>46184</v>
       </c>
       <c r="C56" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2852,10 +2843,10 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C57" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2863,10 +2854,10 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46148</v>
+        <v>46210</v>
       </c>
       <c r="C58" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2874,7 +2865,7 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46175</v>
+        <v>46287</v>
       </c>
       <c r="C59" s="9">
         <v>1</v>
@@ -2885,7 +2876,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2896,7 +2887,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46093</v>
+        <v>46175</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2907,10 +2898,10 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46177</v>
+        <v>46125</v>
       </c>
       <c r="C62" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2918,7 +2909,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2929,10 +2920,10 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46245</v>
+        <v>46177</v>
       </c>
       <c r="C64" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2940,7 +2931,7 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46213</v>
+        <v>46156</v>
       </c>
       <c r="C65" s="9">
         <v>1</v>
@@ -2951,7 +2942,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46092</v>
+        <v>46245</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2962,7 +2953,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46226</v>
+        <v>46213</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2973,7 +2964,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46238</v>
+        <v>46092</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2984,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46188</v>
+        <v>46226</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2995,7 +2986,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46101</v>
+        <v>46238</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -3006,7 +2997,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46261</v>
+        <v>46188</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3014,35 +3005,35 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C72" s="6">
-        <v>76</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46009</v>
+        <v>46261</v>
       </c>
       <c r="C73" s="9">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46000</v>
+        <v>46286</v>
       </c>
       <c r="C74" s="6">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3050,10 +3041,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C75" s="9">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3061,10 +3052,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="C76" s="6">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3072,10 +3063,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="C77" s="9">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3083,10 +3074,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C78" s="6">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3094,10 +3085,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C79" s="9">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3105,10 +3096,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C80" s="6">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3116,10 +3107,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46003</v>
+        <v>46014</v>
       </c>
       <c r="C81" s="9">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3127,10 +3118,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46013</v>
+        <v>46002</v>
       </c>
       <c r="C82" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3138,10 +3129,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46262</v>
+        <v>46008</v>
       </c>
       <c r="C83" s="9">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3149,10 +3140,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46022</v>
+        <v>46003</v>
       </c>
       <c r="C84" s="6">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3160,10 +3151,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C85" s="9">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3171,10 +3162,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46084</v>
+        <v>46022</v>
       </c>
       <c r="C86" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3182,10 +3173,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46125</v>
+        <v>46080</v>
       </c>
       <c r="C87" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3193,10 +3184,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46209</v>
+        <v>46084</v>
       </c>
       <c r="C88" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3204,10 +3195,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C89" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3215,10 +3206,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46083</v>
+        <v>46209</v>
       </c>
       <c r="C90" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3226,10 +3217,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46105</v>
+        <v>46091</v>
       </c>
       <c r="C91" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3237,10 +3228,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46210</v>
+        <v>46083</v>
       </c>
       <c r="C92" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3248,10 +3239,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46211</v>
+        <v>46105</v>
       </c>
       <c r="C93" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3259,10 +3250,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46077</v>
+        <v>46210</v>
       </c>
       <c r="C94" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3270,10 +3261,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46118</v>
+        <v>46211</v>
       </c>
       <c r="C95" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3281,10 +3272,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46078</v>
+        <v>46269</v>
       </c>
       <c r="C96" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3292,10 +3283,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46217</v>
+        <v>46077</v>
       </c>
       <c r="C97" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3303,7 +3294,7 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46099</v>
+        <v>46118</v>
       </c>
       <c r="C98" s="6">
         <v>1</v>
@@ -3314,10 +3305,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46104</v>
+        <v>46078</v>
       </c>
       <c r="C99" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3325,7 +3316,7 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46267</v>
+        <v>46217</v>
       </c>
       <c r="C100" s="6">
         <v>1</v>
@@ -3336,10 +3327,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46248</v>
+        <v>46272</v>
       </c>
       <c r="C101" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3347,7 +3338,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46231</v>
+        <v>46099</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -3358,7 +3349,7 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46258</v>
+        <v>46104</v>
       </c>
       <c r="C103" s="9">
         <v>3</v>
@@ -3369,10 +3360,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46020</v>
+        <v>46267</v>
       </c>
       <c r="C104" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3380,10 +3371,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46076</v>
+        <v>46273</v>
       </c>
       <c r="C105" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3391,10 +3382,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46111</v>
+        <v>46248</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3402,10 +3393,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46087</v>
+        <v>46231</v>
       </c>
       <c r="C107" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3413,10 +3404,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46140</v>
+        <v>46258</v>
       </c>
       <c r="C108" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3424,10 +3415,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46113</v>
+        <v>46020</v>
       </c>
       <c r="C109" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3435,10 +3426,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46119</v>
+        <v>46076</v>
       </c>
       <c r="C110" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3446,7 +3437,7 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C111" s="9">
         <v>1</v>
@@ -3457,10 +3448,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46098</v>
+        <v>46087</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3468,10 +3459,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3479,7 +3470,7 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46079</v>
+        <v>46113</v>
       </c>
       <c r="C114" s="6">
         <v>3</v>
@@ -3490,10 +3481,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46139</v>
+        <v>46119</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3501,10 +3492,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C116" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3512,10 +3503,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46185</v>
+        <v>46274</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3523,7 +3514,7 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46174</v>
+        <v>46098</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -3534,7 +3525,7 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46092</v>
+        <v>46141</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -3545,10 +3536,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46021</v>
+        <v>46287</v>
       </c>
       <c r="C120" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3556,10 +3547,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46177</v>
+        <v>46079</v>
       </c>
       <c r="C121" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3567,10 +3558,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46252</v>
+        <v>46139</v>
       </c>
       <c r="C122" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3578,7 +3569,7 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46212</v>
+        <v>46148</v>
       </c>
       <c r="C123" s="9">
         <v>2</v>
@@ -3589,7 +3580,7 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46269</v>
+        <v>46185</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -3600,10 +3591,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46086</v>
+        <v>46174</v>
       </c>
       <c r="C125" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3611,10 +3602,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46227</v>
+        <v>46286</v>
       </c>
       <c r="C126" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3622,7 +3613,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46188</v>
+        <v>46092</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3633,10 +3624,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46147</v>
+        <v>46021</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3644,7 +3635,7 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46134</v>
+        <v>46177</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3655,10 +3646,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46182</v>
+        <v>46252</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3666,10 +3657,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46190</v>
+        <v>46212</v>
       </c>
       <c r="C131" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3677,87 +3668,87 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46225</v>
+        <v>46086</v>
       </c>
       <c r="C132" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46003</v>
+        <v>46227</v>
       </c>
       <c r="C133" s="9">
-        <v>95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46002</v>
+        <v>46188</v>
       </c>
       <c r="C134" s="6">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46008</v>
+        <v>46147</v>
       </c>
       <c r="C135" s="9">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46000</v>
+        <v>46134</v>
       </c>
       <c r="C136" s="6">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46007</v>
+        <v>46182</v>
       </c>
       <c r="C137" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46001</v>
+        <v>46190</v>
       </c>
       <c r="C138" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46010</v>
+        <v>46225</v>
       </c>
       <c r="C139" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3765,10 +3756,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C140" s="6">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3776,10 +3767,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C141" s="9">
-        <v>2</v>
+        <v>113</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3787,10 +3778,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46014</v>
+        <v>46008</v>
       </c>
       <c r="C142" s="6">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3798,10 +3789,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C143" s="9">
-        <v>2</v>
+        <v>96</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3809,10 +3800,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46021</v>
+        <v>46007</v>
       </c>
       <c r="C144" s="6">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3820,10 +3811,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46212</v>
+        <v>46001</v>
       </c>
       <c r="C145" s="9">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3831,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46077</v>
+        <v>46010</v>
       </c>
       <c r="C146" s="6">
         <v>8</v>
@@ -3842,10 +3833,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46167</v>
+        <v>46006</v>
       </c>
       <c r="C147" s="9">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3853,10 +3844,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46209</v>
+        <v>46009</v>
       </c>
       <c r="C148" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3864,10 +3855,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46189</v>
+        <v>46014</v>
       </c>
       <c r="C149" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3875,10 +3866,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46245</v>
+        <v>46013</v>
       </c>
       <c r="C150" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3886,10 +3877,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46170</v>
+        <v>46021</v>
       </c>
       <c r="C151" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3897,10 +3888,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="C152" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3908,10 +3899,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="C153" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3919,10 +3910,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46233</v>
+        <v>46167</v>
       </c>
       <c r="C154" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3930,10 +3921,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46090</v>
+        <v>46209</v>
       </c>
       <c r="C155" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3941,10 +3932,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46078</v>
+        <v>46189</v>
       </c>
       <c r="C156" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3952,10 +3943,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46084</v>
+        <v>46245</v>
       </c>
       <c r="C157" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3963,10 +3954,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46134</v>
+        <v>46170</v>
       </c>
       <c r="C158" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3974,10 +3965,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46083</v>
+        <v>46210</v>
       </c>
       <c r="C159" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3985,10 +3976,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46262</v>
+        <v>46093</v>
       </c>
       <c r="C160" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3996,10 +3987,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46022</v>
+        <v>46233</v>
       </c>
       <c r="C161" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4007,10 +3998,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46114</v>
+        <v>46090</v>
       </c>
       <c r="C162" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4018,10 +4009,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46135</v>
+        <v>46078</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4029,10 +4020,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46168</v>
+        <v>46084</v>
       </c>
       <c r="C164" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4040,10 +4031,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4051,10 +4042,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4062,10 +4053,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46108</v>
+        <v>46262</v>
       </c>
       <c r="C167" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4073,7 +4064,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46267</v>
+        <v>46022</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4084,10 +4075,10 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46020</v>
+        <v>46114</v>
       </c>
       <c r="C169" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4095,7 +4086,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46248</v>
+        <v>46135</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4106,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46252</v>
+        <v>46287</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4117,7 +4108,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46097</v>
+        <v>46127</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4128,7 +4119,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46177</v>
+        <v>46087</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4139,10 +4130,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46161</v>
+        <v>46286</v>
       </c>
       <c r="C174" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4150,7 +4141,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46129</v>
+        <v>46108</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4161,7 +4152,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46080</v>
+        <v>46267</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4172,7 +4163,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46120</v>
+        <v>46020</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4183,10 +4174,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46101</v>
+        <v>46168</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4194,7 +4185,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46155</v>
+        <v>46248</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4205,7 +4196,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46150</v>
+        <v>46252</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4216,7 +4207,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4227,7 +4218,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46085</v>
+        <v>46177</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4238,10 +4229,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46148</v>
+        <v>46161</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4249,10 +4240,10 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="C184" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4260,10 +4251,10 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46118</v>
+        <v>46080</v>
       </c>
       <c r="C185" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4271,7 +4262,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46258</v>
+        <v>46120</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4282,7 +4273,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46192</v>
+        <v>46101</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4293,7 +4284,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46079</v>
+        <v>46155</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4301,101 +4292,101 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46003</v>
+        <v>46150</v>
       </c>
       <c r="C189" s="9">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46000</v>
+        <v>46141</v>
       </c>
       <c r="C190" s="6">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46006</v>
+        <v>46085</v>
       </c>
       <c r="C191" s="9">
-        <v>167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46001</v>
+        <v>46148</v>
       </c>
       <c r="C192" s="6">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46014</v>
+        <v>46126</v>
       </c>
       <c r="C193" s="9">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46002</v>
+        <v>46118</v>
       </c>
       <c r="C194" s="6">
-        <v>170</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46009</v>
+        <v>46258</v>
       </c>
       <c r="C195" s="9">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46010</v>
+        <v>46192</v>
       </c>
       <c r="C196" s="6">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46008</v>
+        <v>46079</v>
       </c>
       <c r="C197" s="9">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4403,10 +4394,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C198" s="6">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4414,10 +4405,10 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C199" s="9">
-        <v>11</v>
+        <v>132</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4425,10 +4416,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46258</v>
+        <v>46006</v>
       </c>
       <c r="C200" s="6">
-        <v>3</v>
+        <v>167</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4436,10 +4427,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46080</v>
+        <v>46001</v>
       </c>
       <c r="C201" s="9">
-        <v>2</v>
+        <v>173</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4447,10 +4438,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46209</v>
+        <v>46014</v>
       </c>
       <c r="C202" s="6">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4458,10 +4449,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46227</v>
+        <v>46002</v>
       </c>
       <c r="C203" s="9">
-        <v>1</v>
+        <v>170</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4469,10 +4460,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46090</v>
+        <v>46009</v>
       </c>
       <c r="C204" s="6">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4480,10 +4471,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46192</v>
+        <v>46010</v>
       </c>
       <c r="C205" s="9">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4491,10 +4482,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46079</v>
+        <v>46008</v>
       </c>
       <c r="C206" s="6">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4502,10 +4493,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46015</v>
+        <v>46007</v>
       </c>
       <c r="C207" s="9">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4513,10 +4504,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46085</v>
+        <v>46013</v>
       </c>
       <c r="C208" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4524,10 +4515,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46098</v>
+        <v>46258</v>
       </c>
       <c r="C209" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4535,10 +4526,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="C210" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4546,10 +4537,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46265</v>
+        <v>46209</v>
       </c>
       <c r="C211" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4557,10 +4548,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46078</v>
+        <v>46227</v>
       </c>
       <c r="C212" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4568,10 +4559,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46260</v>
+        <v>46090</v>
       </c>
       <c r="C213" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4579,10 +4570,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46128</v>
+        <v>46192</v>
       </c>
       <c r="C214" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4590,10 +4581,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="C215" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4601,10 +4592,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46255</v>
+        <v>46015</v>
       </c>
       <c r="C216" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4612,10 +4603,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46076</v>
+        <v>46085</v>
       </c>
       <c r="C217" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4623,10 +4614,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46262</v>
+        <v>46098</v>
       </c>
       <c r="C218" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4634,10 +4625,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46084</v>
+        <v>46021</v>
       </c>
       <c r="C219" s="9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4645,10 +4636,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46099</v>
+        <v>46265</v>
       </c>
       <c r="C220" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4656,10 +4647,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46154</v>
+        <v>46078</v>
       </c>
       <c r="C221" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4667,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46226</v>
+        <v>46260</v>
       </c>
       <c r="C222" s="6">
         <v>1</v>
@@ -4678,10 +4669,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46092</v>
+        <v>46128</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4689,10 +4680,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4700,7 +4691,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46031</v>
+        <v>46255</v>
       </c>
       <c r="C225" s="9">
         <v>2</v>
@@ -4711,10 +4702,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46120</v>
+        <v>46076</v>
       </c>
       <c r="C226" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4722,10 +4713,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46237</v>
+        <v>46262</v>
       </c>
       <c r="C227" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4733,10 +4724,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46077</v>
+        <v>46084</v>
       </c>
       <c r="C228" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4744,7 +4735,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46114</v>
+        <v>46273</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4755,7 +4746,7 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46216</v>
+        <v>46099</v>
       </c>
       <c r="C230" s="6">
         <v>2</v>
@@ -4766,7 +4757,7 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46037</v>
+        <v>46154</v>
       </c>
       <c r="C231" s="9">
         <v>1</v>
@@ -4777,10 +4768,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46020</v>
+        <v>46226</v>
       </c>
       <c r="C232" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4788,7 +4779,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46106</v>
+        <v>46092</v>
       </c>
       <c r="C233" s="9">
         <v>1</v>
@@ -4799,7 +4790,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46211</v>
+        <v>46022</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4810,10 +4801,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46239</v>
+        <v>46120</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4821,10 +4812,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46155</v>
+        <v>46237</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4832,10 +4823,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46210</v>
+        <v>46077</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4843,7 +4834,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -4854,10 +4845,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46132</v>
+        <v>46216</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4865,7 +4856,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46108</v>
+        <v>46037</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -4876,7 +4867,7 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46148</v>
+        <v>46276</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -4887,10 +4878,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46118</v>
+        <v>46020</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4898,7 +4889,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46035</v>
+        <v>46106</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4909,10 +4900,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46181</v>
+        <v>46287</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4920,7 +4911,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46087</v>
+        <v>46211</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4931,10 +4922,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46030</v>
+        <v>46239</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4942,7 +4933,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46204</v>
+        <v>46155</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -4953,10 +4944,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46176</v>
+        <v>46210</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4964,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46101</v>
+        <v>46112</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4975,7 +4966,7 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46213</v>
+        <v>46132</v>
       </c>
       <c r="C250" s="6">
         <v>1</v>
@@ -4986,7 +4977,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4994,145 +4985,145 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46001</v>
+        <v>46148</v>
       </c>
       <c r="C252" s="6">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46008</v>
+        <v>46118</v>
       </c>
       <c r="C253" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46003</v>
+        <v>46035</v>
       </c>
       <c r="C254" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46002</v>
+        <v>46181</v>
       </c>
       <c r="C255" s="9">
-        <v>109</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46006</v>
+        <v>46087</v>
       </c>
       <c r="C256" s="6">
-        <v>145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46007</v>
+        <v>46030</v>
       </c>
       <c r="C257" s="9">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46000</v>
+        <v>46031</v>
       </c>
       <c r="C258" s="6">
-        <v>127</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46084</v>
+        <v>46204</v>
       </c>
       <c r="C259" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46013</v>
+        <v>46176</v>
       </c>
       <c r="C260" s="6">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46010</v>
+        <v>46286</v>
       </c>
       <c r="C261" s="9">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46021</v>
+        <v>46101</v>
       </c>
       <c r="C262" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46009</v>
+        <v>46213</v>
       </c>
       <c r="C263" s="9">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46083</v>
+        <v>46142</v>
       </c>
       <c r="C264" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5140,10 +5131,10 @@
         <v>21</v>
       </c>
       <c r="B265" s="8">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C265" s="9">
-        <v>20</v>
+        <v>151</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5151,10 +5142,10 @@
         <v>21</v>
       </c>
       <c r="B266" s="5">
-        <v>46157</v>
+        <v>46008</v>
       </c>
       <c r="C266" s="6">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -5162,10 +5153,10 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46079</v>
+        <v>46003</v>
       </c>
       <c r="C267" s="9">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -5173,10 +5164,10 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46167</v>
+        <v>46002</v>
       </c>
       <c r="C268" s="6">
-        <v>1</v>
+        <v>109</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5184,10 +5175,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46035</v>
+        <v>46006</v>
       </c>
       <c r="C269" s="9">
-        <v>2</v>
+        <v>145</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5195,10 +5186,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46085</v>
+        <v>46007</v>
       </c>
       <c r="C270" s="6">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5206,10 +5197,10 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46120</v>
+        <v>46000</v>
       </c>
       <c r="C271" s="9">
-        <v>2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5217,10 +5208,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46114</v>
+        <v>46084</v>
       </c>
       <c r="C272" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5228,10 +5219,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46094</v>
+        <v>46013</v>
       </c>
       <c r="C273" s="9">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5239,10 +5230,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46192</v>
+        <v>46010</v>
       </c>
       <c r="C274" s="6">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5250,10 +5241,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46080</v>
+        <v>46021</v>
       </c>
       <c r="C275" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5261,10 +5252,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46127</v>
+        <v>46009</v>
       </c>
       <c r="C276" s="6">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5272,10 +5263,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="C277" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5283,10 +5274,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46090</v>
+        <v>46014</v>
       </c>
       <c r="C278" s="6">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5294,7 +5285,7 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46020</v>
+        <v>46157</v>
       </c>
       <c r="C279" s="9">
         <v>2</v>
@@ -5305,10 +5296,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C280" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5316,7 +5307,7 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46217</v>
+        <v>46167</v>
       </c>
       <c r="C281" s="9">
         <v>1</v>
@@ -5327,10 +5318,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46078</v>
+        <v>46035</v>
       </c>
       <c r="C282" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5338,10 +5329,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46209</v>
+        <v>46085</v>
       </c>
       <c r="C283" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5349,10 +5340,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46237</v>
+        <v>46120</v>
       </c>
       <c r="C284" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5360,10 +5351,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46148</v>
+        <v>46114</v>
       </c>
       <c r="C285" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5371,10 +5362,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46105</v>
+        <v>46094</v>
       </c>
       <c r="C286" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5382,10 +5373,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46087</v>
+        <v>46192</v>
       </c>
       <c r="C287" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5393,10 +5384,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46107</v>
+        <v>46080</v>
       </c>
       <c r="C288" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5404,10 +5395,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46086</v>
+        <v>46127</v>
       </c>
       <c r="C289" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5415,10 +5406,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46106</v>
+        <v>46091</v>
       </c>
       <c r="C290" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5426,10 +5417,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46150</v>
+        <v>46090</v>
       </c>
       <c r="C291" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5437,10 +5428,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46104</v>
+        <v>46020</v>
       </c>
       <c r="C292" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5448,10 +5439,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46118</v>
+        <v>46015</v>
       </c>
       <c r="C293" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5459,7 +5450,7 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46231</v>
+        <v>46217</v>
       </c>
       <c r="C294" s="6">
         <v>1</v>
@@ -5470,10 +5461,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="C295" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5481,10 +5472,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46182</v>
+        <v>46209</v>
       </c>
       <c r="C296" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5492,7 +5483,7 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46188</v>
+        <v>46237</v>
       </c>
       <c r="C297" s="9">
         <v>1</v>
@@ -5503,10 +5494,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46154</v>
+        <v>46148</v>
       </c>
       <c r="C298" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5514,10 +5505,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="C299" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5525,10 +5516,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46122</v>
+        <v>46087</v>
       </c>
       <c r="C300" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5536,7 +5527,7 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46092</v>
+        <v>46107</v>
       </c>
       <c r="C301" s="9">
         <v>3</v>
@@ -5547,10 +5538,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46156</v>
+        <v>46086</v>
       </c>
       <c r="C302" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5558,7 +5549,7 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46133</v>
+        <v>46106</v>
       </c>
       <c r="C303" s="9">
         <v>1</v>
@@ -5569,10 +5560,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46189</v>
+        <v>46150</v>
       </c>
       <c r="C304" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5580,10 +5571,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46210</v>
+        <v>46104</v>
       </c>
       <c r="C305" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5591,7 +5582,7 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46232</v>
+        <v>46118</v>
       </c>
       <c r="C306" s="6">
         <v>1</v>
@@ -5602,7 +5593,7 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46126</v>
+        <v>46231</v>
       </c>
       <c r="C307" s="9">
         <v>1</v>
@@ -5613,10 +5604,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46022</v>
+        <v>46076</v>
       </c>
       <c r="C308" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5624,10 +5615,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46100</v>
+        <v>46182</v>
       </c>
       <c r="C309" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5635,7 +5626,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C310" s="6">
         <v>1</v>
@@ -5646,10 +5637,10 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46097</v>
+        <v>46154</v>
       </c>
       <c r="C311" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -5657,7 +5648,7 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46077</v>
+        <v>46093</v>
       </c>
       <c r="C312" s="6">
         <v>3</v>
@@ -5668,7 +5659,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46108</v>
+        <v>46122</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5679,10 +5670,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46233</v>
+        <v>46092</v>
       </c>
       <c r="C314" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5690,7 +5681,7 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46098</v>
+        <v>46156</v>
       </c>
       <c r="C315" s="9">
         <v>2</v>
@@ -5701,7 +5692,7 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46113</v>
+        <v>46287</v>
       </c>
       <c r="C316" s="6">
         <v>1</v>
@@ -5712,7 +5703,7 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46253</v>
+        <v>46133</v>
       </c>
       <c r="C317" s="9">
         <v>1</v>
@@ -5723,7 +5714,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46142</v>
+        <v>46189</v>
       </c>
       <c r="C318" s="6">
         <v>1</v>
@@ -5734,7 +5725,7 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46244</v>
+        <v>46210</v>
       </c>
       <c r="C319" s="9">
         <v>1</v>
@@ -5745,7 +5736,7 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46153</v>
+        <v>46232</v>
       </c>
       <c r="C320" s="6">
         <v>1</v>
@@ -5756,7 +5747,7 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46031</v>
+        <v>46126</v>
       </c>
       <c r="C321" s="9">
         <v>1</v>
@@ -5767,9 +5758,163 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
+        <v>46022</v>
+      </c>
+      <c r="C322" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B323" s="8">
+        <v>46100</v>
+      </c>
+      <c r="C323" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B324" s="5">
+        <v>46101</v>
+      </c>
+      <c r="C324" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B325" s="8">
+        <v>46097</v>
+      </c>
+      <c r="C325" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B326" s="5">
+        <v>46077</v>
+      </c>
+      <c r="C326" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B327" s="8">
+        <v>46108</v>
+      </c>
+      <c r="C327" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B328" s="5">
+        <v>46233</v>
+      </c>
+      <c r="C328" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B329" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C329" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B330" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C330" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B331" s="8">
+        <v>46253</v>
+      </c>
+      <c r="C331" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B332" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C332" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B333" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C333" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B334" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C334" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C335" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B336" s="5">
         <v>46155</v>
       </c>
-      <c r="C322" s="6">
+      <c r="C336" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5935,7 +6080,7 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -5958,7 +6103,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5989,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6026,7 +6171,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6043,7 +6188,7 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -6060,7 +6205,7 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -6071,13 +6216,13 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -6088,13 +6233,13 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -6105,13 +6250,13 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6128,7 +6273,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -6179,7 +6324,7 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -6224,7 +6369,7 @@
         <v>11</v>
       </c>
       <c r="C26">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -6247,7 +6392,7 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -6264,7 +6409,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6315,7 +6460,7 @@
         <v>5</v>
       </c>
       <c r="E31">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -6329,10 +6474,10 @@
         <v>81</v>
       </c>
       <c r="D32">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E32">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6343,7 +6488,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D33">
         <v>7</v>
@@ -6377,7 +6522,7 @@
         <v>20</v>
       </c>
       <c r="C35">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -6397,7 +6542,7 @@
         <v>107</v>
       </c>
       <c r="D36">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36">
         <v>65</v>
@@ -6434,7 +6579,7 @@
         <v>10</v>
       </c>
       <c r="E38">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6477,7 +6622,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6532,7 +6677,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -6543,7 +6688,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -6554,10 +6699,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -6565,7 +6710,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -6576,7 +6721,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -6587,7 +6732,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -6598,7 +6743,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6609,7 +6754,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6840,7 +6985,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6906,7 +7051,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C40">
         <v>11</v>
@@ -6961,7 +7106,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -6972,7 +7117,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -7005,7 +7150,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -7016,7 +7161,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -7027,7 +7172,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -7038,7 +7183,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -7049,7 +7194,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -7060,7 +7205,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -7071,7 +7216,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -7082,7 +7227,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -7093,7 +7238,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -7115,7 +7260,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -7137,7 +7282,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>237</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7159,7 +7304,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -7170,7 +7315,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -7181,10 +7326,10 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -7192,7 +7337,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7203,7 +7348,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7214,7 +7359,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7225,7 +7370,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7236,7 +7381,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7247,7 +7392,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7258,7 +7403,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7269,7 +7414,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7280,7 +7425,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7291,7 +7436,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7302,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7313,7 +7458,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7324,7 +7469,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7335,7 +7480,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7346,7 +7491,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7357,7 +7502,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -7379,7 +7524,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7390,7 +7535,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7401,7 +7546,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -7412,7 +7557,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7423,7 +7568,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7434,7 +7579,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7445,7 +7590,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -7456,7 +7601,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7467,7 +7612,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7478,7 +7623,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7489,7 +7634,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7500,7 +7645,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7511,7 +7656,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7522,7 +7667,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7533,7 +7678,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7544,7 +7689,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7555,7 +7700,7 @@
         <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7566,7 +7711,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -7574,13 +7719,13 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B101" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C101">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -7588,10 +7733,10 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C102">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -7599,10 +7744,10 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C103">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -7610,10 +7755,10 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -7621,10 +7766,10 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -7643,7 +7788,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="C107">
         <v>6</v>
@@ -7654,10 +7799,10 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -7665,10 +7810,10 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C109">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -7679,7 +7824,7 @@
         <v>123</v>
       </c>
       <c r="C110">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -7687,7 +7832,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -7698,7 +7843,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -7709,7 +7854,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -7720,7 +7865,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -7731,7 +7876,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -7742,10 +7887,10 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C116">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -7764,7 +7909,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C118">
         <v>3</v>
@@ -7775,10 +7920,10 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -7786,10 +7931,10 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -7808,7 +7953,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7819,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7830,7 +7975,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7841,7 +7986,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7852,7 +7997,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7885,7 +8030,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -7907,10 +8052,10 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -7918,7 +8063,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7929,7 +8074,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -7940,7 +8085,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7951,7 +8096,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7962,7 +8107,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7973,7 +8118,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7984,7 +8129,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7995,7 +8140,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8006,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8017,7 +8162,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -8028,7 +8173,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8039,7 +8184,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -8050,7 +8195,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -8061,7 +8206,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -8072,7 +8217,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8083,7 +8228,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8094,7 +8239,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8105,7 +8250,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8116,7 +8261,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8127,7 +8272,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8138,7 +8283,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8149,7 +8294,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8160,7 +8305,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8171,7 +8316,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8182,7 +8327,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8193,7 +8338,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -8204,7 +8349,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -8215,7 +8360,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8226,7 +8371,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8237,7 +8382,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8259,7 +8404,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8270,7 +8415,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8281,7 +8426,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8292,7 +8437,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8303,7 +8448,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8314,7 +8459,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8325,7 +8470,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8336,7 +8481,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8347,7 +8492,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8358,7 +8503,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8369,7 +8514,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8380,7 +8525,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8391,7 +8536,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8402,7 +8547,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8413,7 +8558,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8424,7 +8569,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8435,7 +8580,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8446,7 +8591,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>138</v>
+        <v>67</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8457,7 +8602,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8468,7 +8613,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8479,7 +8624,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8490,7 +8635,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8501,7 +8646,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8509,24 +8654,24 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="C186">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C187">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8534,10 +8679,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C188">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8545,10 +8690,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C189">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8556,10 +8701,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="C190">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -8567,10 +8712,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="C191">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -8578,10 +8723,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="C192">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8589,10 +8734,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C193">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8600,10 +8745,10 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="C194">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -8611,10 +8756,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="C195">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8622,10 +8767,10 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C196">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -8633,10 +8778,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C197">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -8644,10 +8789,10 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C198">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -8655,10 +8800,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="C199">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8666,10 +8811,10 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="C200">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -8677,10 +8822,10 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>65</v>
+        <v>189</v>
       </c>
       <c r="C201">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -8688,10 +8833,10 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="C202">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -8699,10 +8844,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8710,10 +8855,10 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>57</v>
+        <v>191</v>
       </c>
       <c r="C204">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -8721,10 +8866,10 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C205">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -8732,10 +8877,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C206">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -8743,10 +8888,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8754,7 +8899,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -8765,7 +8910,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8776,7 +8921,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C210">
         <v>5</v>
@@ -8787,10 +8932,10 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C211">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -8798,7 +8943,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8809,7 +8954,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8820,7 +8965,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -8831,10 +8976,10 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C215">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -8842,10 +8987,10 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>195</v>
+        <v>73</v>
       </c>
       <c r="C216">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -8853,7 +8998,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8864,7 +9009,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8875,7 +9020,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8897,7 +9042,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8908,7 +9053,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -8919,7 +9064,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -8941,10 +9086,10 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C225">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -8952,10 +9097,10 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>199</v>
+        <v>286</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -8963,7 +9108,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8985,7 +9130,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8996,7 +9141,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9007,7 +9152,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9018,10 +9163,10 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -9029,10 +9174,10 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -9040,7 +9185,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -9051,7 +9196,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9062,7 +9207,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9073,7 +9218,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9084,7 +9229,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9095,7 +9240,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9106,7 +9251,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>123</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9128,7 +9273,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9150,7 +9295,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9161,7 +9306,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9172,7 +9317,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9183,7 +9328,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9194,7 +9339,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9205,7 +9350,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9216,7 +9361,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9227,7 +9372,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9238,7 +9383,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9249,7 +9394,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9260,7 +9405,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9271,7 +9416,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9282,7 +9427,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9293,7 +9438,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9304,7 +9449,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>112</v>
+        <v>218</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9315,7 +9460,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9326,7 +9471,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9337,7 +9482,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9348,7 +9493,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9359,7 +9504,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9370,7 +9515,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9381,7 +9526,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9392,7 +9537,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9403,7 +9548,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9414,7 +9559,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9425,7 +9570,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9436,7 +9581,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9447,7 +9592,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9458,7 +9603,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9466,13 +9611,13 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>118</v>
+        <v>213</v>
       </c>
       <c r="C273">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -9480,10 +9625,10 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C274">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -9491,10 +9636,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="C275">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -9502,10 +9647,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="C276">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -9513,10 +9658,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>196</v>
+        <v>101</v>
       </c>
       <c r="C277">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -9524,10 +9669,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="C278">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -9535,7 +9680,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="C279">
         <v>6</v>
@@ -9546,10 +9691,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C280">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -9557,7 +9702,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -9568,7 +9713,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>125</v>
+        <v>236</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9579,7 +9724,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9590,7 +9735,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9601,7 +9746,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>237</v>
+        <v>125</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -9612,10 +9757,10 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C286">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -9623,7 +9768,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -9634,10 +9779,10 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C288">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -9645,7 +9790,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -9656,7 +9801,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9667,7 +9812,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9678,7 +9823,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9689,7 +9834,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9700,7 +9845,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9711,7 +9856,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9722,7 +9867,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9733,7 +9878,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9744,7 +9889,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9755,7 +9900,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9766,10 +9911,10 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C300">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -9777,7 +9922,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9788,7 +9933,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>168</v>
+        <v>259</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9799,7 +9944,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9810,7 +9955,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>245</v>
+        <v>84</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9821,7 +9966,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9832,7 +9977,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9843,7 +9988,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9854,7 +9999,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>54</v>
+        <v>245</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9865,7 +10010,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>247</v>
+        <v>122</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9876,7 +10021,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9887,7 +10032,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9898,7 +10043,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9909,7 +10054,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9920,7 +10065,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9931,7 +10076,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -9942,10 +10087,10 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="C316">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -9953,7 +10098,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9964,7 +10109,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9975,7 +10120,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9986,7 +10131,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9997,7 +10142,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10008,7 +10153,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>259</v>
+        <v>134</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10019,7 +10164,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>134</v>
+        <v>260</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10030,7 +10175,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10041,7 +10186,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10052,7 +10197,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10063,7 +10208,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10074,7 +10219,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10085,7 +10230,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>144</v>
+        <v>254</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10096,7 +10241,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10107,7 +10252,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10118,7 +10263,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10129,7 +10274,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>269</v>
+        <v>63</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10140,7 +10285,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>112</v>
+        <v>255</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10151,7 +10296,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>116</v>
+        <v>268</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10162,7 +10307,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>255</v>
+        <v>116</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -10173,7 +10318,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10184,7 +10329,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10195,7 +10340,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10206,7 +10351,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10217,7 +10362,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10228,7 +10373,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>248</v>
+        <v>168</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10239,7 +10384,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>169</v>
+        <v>264</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10261,7 +10406,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10272,7 +10417,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>262</v>
+        <v>49</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10283,7 +10428,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10294,7 +10439,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>161</v>
+        <v>261</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10305,7 +10450,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10316,7 +10461,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -10360,7 +10505,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10371,7 +10516,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10382,7 +10527,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10393,7 +10538,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10404,7 +10549,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10415,7 +10560,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10426,7 +10571,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10437,7 +10582,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10448,7 +10593,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10459,7 +10604,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -10484,10 +10629,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10495,7 +10640,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C2">
         <v>66</v>
@@ -10506,10 +10651,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C3">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10517,7 +10662,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -10528,10 +10673,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10539,7 +10684,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -10550,7 +10695,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -10561,7 +10706,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -10572,10 +10717,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C9">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10583,10 +10728,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10594,7 +10739,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C11">
         <v>29</v>
@@ -10605,10 +10750,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -10616,7 +10761,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -10627,10 +10772,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C14">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10638,7 +10783,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -10649,10 +10794,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -10660,10 +10805,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C17">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -10671,10 +10816,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C18">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -10682,7 +10827,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -10693,7 +10838,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -10704,7 +10849,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -10715,7 +10860,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -10726,7 +10871,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -10737,7 +10882,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C24">
         <v>40</v>
@@ -10748,10 +10893,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C25">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10759,7 +10904,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -10770,10 +10915,10 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C27">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -10781,7 +10926,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C28">
         <v>140</v>
@@ -10792,7 +10937,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C29">
         <v>79</v>
@@ -10803,7 +10948,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -10814,7 +10959,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10825,7 +10970,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -10836,7 +10981,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10847,7 +10992,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C34">
         <v>704</v>
@@ -10858,7 +11003,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -10869,7 +11014,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C36">
         <v>22</v>
@@ -10880,7 +11025,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C37">
         <v>62</v>
@@ -10891,7 +11036,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C38">
         <v>58</v>
@@ -10902,7 +11047,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C39">
         <v>25</v>
@@ -10913,7 +11058,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -10924,7 +11069,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -10935,7 +11080,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -10946,7 +11091,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -10978,7 +11123,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11085,7 +11230,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -11195,7 +11340,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -11305,7 +11450,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="565" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF99CF4A-C45E-4AE5-A8A4-3EEF35653D76}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F5C7921-131F-464F-A566-82208D75264B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -500,9 +500,6 @@
   </si>
   <si>
     <t>Escuela de Lenguaje Yamanqui</t>
-  </si>
-  <si>
-    <t>Escuela República del Ecuador</t>
   </si>
   <si>
     <t>Colegio Madres Dominicas</t>
@@ -1038,6 +1035,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1773,10 +1774,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14">
-        <v>1.081</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1977,10 +1978,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.98799999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1994,10 +1995,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E27">
-        <v>0.97199999999999998</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2096,10 +2097,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.0329999999999999</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2214,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C336"/>
+  <dimension ref="A1:C338"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2876,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46148</v>
+        <v>46289</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2887,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2898,7 +2899,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -2909,7 +2910,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2920,10 +2921,10 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C64" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2931,10 +2932,10 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C65" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2942,7 +2943,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2953,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2964,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2975,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2986,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -2997,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3008,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3019,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3030,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3038,13 +3039,13 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C75" s="9">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3052,10 +3053,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C76" s="6">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3063,10 +3064,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C77" s="9">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3074,10 +3075,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C78" s="6">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3085,10 +3086,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C79" s="9">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3096,10 +3097,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C80" s="6">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3107,10 +3108,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C81" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3118,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C82" s="6">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3129,10 +3130,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C83" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3140,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C84" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3151,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C85" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3162,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C86" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3173,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C87" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3184,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C88" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3195,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C89" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3206,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C90" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3217,7 +3218,7 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C91" s="9">
         <v>2</v>
@@ -3228,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C92" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3239,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C93" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3250,7 +3251,7 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
@@ -3261,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C95" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3272,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C96" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3283,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C97" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3294,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C98" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3305,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C99" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3316,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46217</v>
+        <v>46078</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3327,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46272</v>
+        <v>46217</v>
       </c>
       <c r="C101" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3338,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C102" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3349,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C103" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3360,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C104" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3371,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C105" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3382,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C106" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3393,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C107" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3404,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C108" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3415,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C109" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3426,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C110" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3437,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C111" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3448,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3459,7 +3460,7 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C113" s="9">
         <v>2</v>
@@ -3470,10 +3471,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C114" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3481,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C115" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3492,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3503,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3514,10 +3515,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3525,7 +3526,7 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -3536,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3547,10 +3548,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3558,10 +3559,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3569,10 +3570,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C123" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3580,10 +3581,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3591,7 +3592,7 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3602,7 +3603,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3613,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3624,10 +3625,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C128" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3635,10 +3636,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C129" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3646,10 +3647,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C130" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3657,10 +3658,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C131" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3668,10 +3669,10 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46086</v>
+        <v>46212</v>
       </c>
       <c r="C132" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3679,10 +3680,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46227</v>
+        <v>46288</v>
       </c>
       <c r="C133" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3690,10 +3691,10 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46188</v>
+        <v>46086</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3701,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46147</v>
+        <v>46227</v>
       </c>
       <c r="C135" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3712,7 +3713,7 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46134</v>
+        <v>46188</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3723,7 +3724,7 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3734,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46190</v>
+        <v>46134</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3745,7 +3746,7 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46225</v>
+        <v>46182</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3753,24 +3754,24 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46003</v>
+        <v>46190</v>
       </c>
       <c r="C140" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="C141" s="9">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3778,10 +3779,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C142" s="6">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3789,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C143" s="9">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3800,10 +3801,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C144" s="6">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3811,10 +3812,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C145" s="9">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3822,10 +3823,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C146" s="6">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3833,10 +3834,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C147" s="9">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3844,10 +3845,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C148" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3855,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C149" s="9">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3866,7 +3867,7 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C150" s="6">
         <v>2</v>
@@ -3877,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C151" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3888,7 +3889,7 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46212</v>
+        <v>46013</v>
       </c>
       <c r="C152" s="6">
         <v>2</v>
@@ -3899,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C153" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3910,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="C154" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3921,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46209</v>
+        <v>46077</v>
       </c>
       <c r="C155" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3932,10 +3933,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="C156" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3943,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3954,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C158" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3965,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C159" s="9">
         <v>1</v>
@@ -3976,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C160" s="6">
         <v>1</v>
@@ -3987,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C161" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3998,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C162" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4009,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C163" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4020,7 +4021,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C164" s="6">
         <v>4</v>
@@ -4031,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C165" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4042,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C166" s="6">
         <v>4</v>
@@ -4053,7 +4054,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46262</v>
+        <v>46134</v>
       </c>
       <c r="C167" s="9">
         <v>2</v>
@@ -4064,10 +4065,10 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C168" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4075,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46114</v>
+        <v>46262</v>
       </c>
       <c r="C169" s="9">
         <v>2</v>
@@ -4086,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4097,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46287</v>
+        <v>46114</v>
       </c>
       <c r="C171" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4108,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4119,7 +4120,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46087</v>
+        <v>46287</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4130,7 +4131,7 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46286</v>
+        <v>46127</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4141,7 +4142,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4152,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46267</v>
+        <v>46286</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4163,7 +4164,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4174,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46168</v>
+        <v>46267</v>
       </c>
       <c r="C178" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4185,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46248</v>
+        <v>46020</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4196,10 +4197,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46252</v>
+        <v>46168</v>
       </c>
       <c r="C180" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4207,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46097</v>
+        <v>46248</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4218,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46177</v>
+        <v>46252</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4229,10 +4230,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C183" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4240,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46129</v>
+        <v>46177</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4251,10 +4252,10 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46080</v>
+        <v>46161</v>
       </c>
       <c r="C185" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4262,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46120</v>
+        <v>46129</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4273,7 +4274,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4284,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46155</v>
+        <v>46120</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4295,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4306,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4317,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46085</v>
+        <v>46150</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4328,7 +4329,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4339,10 +4340,10 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46126</v>
+        <v>46085</v>
       </c>
       <c r="C193" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4350,10 +4351,10 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C194" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4361,10 +4362,10 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46258</v>
+        <v>46126</v>
       </c>
       <c r="C195" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4372,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46192</v>
+        <v>46118</v>
       </c>
       <c r="C196" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4383,7 +4384,7 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46079</v>
+        <v>46258</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4391,24 +4392,24 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46003</v>
+        <v>46192</v>
       </c>
       <c r="C198" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C199" s="9">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4416,10 +4417,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C200" s="6">
-        <v>167</v>
+        <v>91</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4427,10 +4428,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C201" s="9">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4438,10 +4439,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C202" s="6">
-        <v>15</v>
+        <v>167</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4449,10 +4450,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C203" s="9">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4460,10 +4461,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C204" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4471,10 +4472,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C205" s="9">
-        <v>18</v>
+        <v>168</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4482,10 +4483,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C206" s="6">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4493,10 +4494,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C207" s="9">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4504,10 +4505,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C208" s="6">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4515,10 +4516,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46258</v>
+        <v>46007</v>
       </c>
       <c r="C209" s="9">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4526,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C210" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4537,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46209</v>
+        <v>46258</v>
       </c>
       <c r="C211" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4548,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46227</v>
+        <v>46080</v>
       </c>
       <c r="C212" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4559,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46090</v>
+        <v>46209</v>
       </c>
       <c r="C213" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4570,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="C214" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4581,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C215" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4592,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46015</v>
+        <v>46192</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4603,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C217" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4614,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C218" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4625,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="C219" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4636,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46265</v>
+        <v>46098</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4647,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C221" s="9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4658,7 +4659,7 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C222" s="6">
         <v>1</v>
@@ -4669,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C223" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4680,10 +4681,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46083</v>
+        <v>46260</v>
       </c>
       <c r="C224" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4691,10 +4692,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46255</v>
+        <v>46128</v>
       </c>
       <c r="C225" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4702,7 +4703,7 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C226" s="6">
         <v>7</v>
@@ -4713,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4724,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="C228" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4735,7 +4736,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4746,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="C230" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4757,7 +4758,7 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46154</v>
+        <v>46273</v>
       </c>
       <c r="C231" s="9">
         <v>1</v>
@@ -4768,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46226</v>
+        <v>46099</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4779,7 +4780,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C233" s="9">
         <v>1</v>
@@ -4790,7 +4791,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46022</v>
+        <v>46226</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4801,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46120</v>
+        <v>46092</v>
       </c>
       <c r="C235" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4812,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46237</v>
+        <v>46022</v>
       </c>
       <c r="C236" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4823,10 +4824,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C237" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4834,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46114</v>
+        <v>46237</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4845,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46216</v>
+        <v>46077</v>
       </c>
       <c r="C239" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4856,7 +4857,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -4867,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46276</v>
+        <v>46216</v>
       </c>
       <c r="C241" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4878,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C242" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4889,7 +4890,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46106</v>
+        <v>46276</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4900,10 +4901,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46287</v>
+        <v>46020</v>
       </c>
       <c r="C244" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4911,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46211</v>
+        <v>46106</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4922,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46239</v>
+        <v>46287</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4933,7 +4934,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46155</v>
+        <v>46211</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -4944,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46210</v>
+        <v>46239</v>
       </c>
       <c r="C248" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4955,7 +4956,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4966,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46132</v>
+        <v>46210</v>
       </c>
       <c r="C250" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4977,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4988,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46148</v>
+        <v>46132</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -4999,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46118</v>
+        <v>46108</v>
       </c>
       <c r="C253" s="9">
         <v>1</v>
@@ -5010,7 +5011,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46035</v>
+        <v>46148</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5021,7 +5022,7 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46181</v>
+        <v>46118</v>
       </c>
       <c r="C255" s="9">
         <v>1</v>
@@ -5032,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46087</v>
+        <v>46035</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5043,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46030</v>
+        <v>46181</v>
       </c>
       <c r="C257" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5054,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46031</v>
+        <v>46087</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5065,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46204</v>
+        <v>46030</v>
       </c>
       <c r="C259" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5076,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46176</v>
+        <v>46031</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
@@ -5087,7 +5088,7 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46286</v>
+        <v>46204</v>
       </c>
       <c r="C261" s="9">
         <v>1</v>
@@ -5098,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46101</v>
+        <v>46176</v>
       </c>
       <c r="C262" s="6">
         <v>1</v>
@@ -5109,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46213</v>
+        <v>46286</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5120,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5128,24 +5129,24 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46001</v>
+        <v>46213</v>
       </c>
       <c r="C265" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C266" s="6">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -5153,10 +5154,10 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C267" s="9">
-        <v>70</v>
+        <v>151</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -5164,10 +5165,10 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C268" s="6">
-        <v>109</v>
+        <v>38</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5175,10 +5176,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C269" s="9">
-        <v>145</v>
+        <v>70</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5186,10 +5187,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C270" s="6">
-        <v>45</v>
+        <v>109</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5197,10 +5198,10 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C271" s="9">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5208,10 +5209,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C272" s="6">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5219,10 +5220,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C273" s="9">
-        <v>25</v>
+        <v>127</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5230,10 +5231,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="C274" s="6">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5241,10 +5242,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C275" s="9">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5252,10 +5253,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C276" s="6">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5263,10 +5264,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C277" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5274,10 +5275,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C278" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5285,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C279" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5296,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46079</v>
+        <v>46014</v>
       </c>
       <c r="C280" s="6">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5307,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="C281" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5318,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="C282" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5329,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46085</v>
+        <v>46167</v>
       </c>
       <c r="C283" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5340,7 +5341,7 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46120</v>
+        <v>46035</v>
       </c>
       <c r="C284" s="6">
         <v>2</v>
@@ -5351,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46114</v>
+        <v>46085</v>
       </c>
       <c r="C285" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5362,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="C286" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5373,7 +5374,7 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46192</v>
+        <v>46114</v>
       </c>
       <c r="C287" s="9">
         <v>1</v>
@@ -5384,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C288" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5395,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46127</v>
+        <v>46192</v>
       </c>
       <c r="C289" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5406,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="C290" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5417,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46090</v>
+        <v>46127</v>
       </c>
       <c r="C291" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5428,7 +5429,7 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46020</v>
+        <v>46091</v>
       </c>
       <c r="C292" s="6">
         <v>2</v>
@@ -5439,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C293" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5450,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46217</v>
+        <v>46020</v>
       </c>
       <c r="C294" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5461,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C295" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5472,10 +5473,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46209</v>
+        <v>46217</v>
       </c>
       <c r="C296" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5483,10 +5484,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46237</v>
+        <v>46078</v>
       </c>
       <c r="C297" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5494,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46148</v>
+        <v>46209</v>
       </c>
       <c r="C298" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5505,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46105</v>
+        <v>46237</v>
       </c>
       <c r="C299" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5516,10 +5517,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46087</v>
+        <v>46148</v>
       </c>
       <c r="C300" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5527,10 +5528,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="C301" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5538,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="C302" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5549,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C303" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5560,10 +5561,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46150</v>
+        <v>46086</v>
       </c>
       <c r="C304" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5571,10 +5572,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="C305" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5582,10 +5583,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46118</v>
+        <v>46150</v>
       </c>
       <c r="C306" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5593,10 +5594,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46231</v>
+        <v>46104</v>
       </c>
       <c r="C307" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5604,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C308" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5615,7 +5616,7 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46182</v>
+        <v>46231</v>
       </c>
       <c r="C309" s="9">
         <v>1</v>
@@ -5626,10 +5627,10 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46188</v>
+        <v>46076</v>
       </c>
       <c r="C310" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -5637,7 +5638,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="C311" s="9">
         <v>1</v>
@@ -5648,10 +5649,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46093</v>
+        <v>46188</v>
       </c>
       <c r="C312" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5659,7 +5660,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5670,7 +5671,7 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C314" s="6">
         <v>3</v>
@@ -5681,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C315" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5692,10 +5693,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46287</v>
+        <v>46092</v>
       </c>
       <c r="C316" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5703,10 +5704,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="C317" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5714,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46189</v>
+        <v>46287</v>
       </c>
       <c r="C318" s="6">
         <v>1</v>
@@ -5725,7 +5726,7 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46210</v>
+        <v>46133</v>
       </c>
       <c r="C319" s="9">
         <v>1</v>
@@ -5736,7 +5737,7 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46232</v>
+        <v>46189</v>
       </c>
       <c r="C320" s="6">
         <v>1</v>
@@ -5747,7 +5748,7 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46126</v>
+        <v>46210</v>
       </c>
       <c r="C321" s="9">
         <v>1</v>
@@ -5758,7 +5759,7 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46022</v>
+        <v>46232</v>
       </c>
       <c r="C322" s="6">
         <v>1</v>
@@ -5769,10 +5770,10 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46100</v>
+        <v>46126</v>
       </c>
       <c r="C323" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -5780,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5791,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C325" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5802,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46077</v>
+        <v>46101</v>
       </c>
       <c r="C326" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5813,10 +5814,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C327" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5824,10 +5825,10 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46233</v>
+        <v>46077</v>
       </c>
       <c r="C328" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -5835,10 +5836,10 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C329" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -5846,7 +5847,7 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46113</v>
+        <v>46233</v>
       </c>
       <c r="C330" s="6">
         <v>1</v>
@@ -5857,10 +5858,10 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46253</v>
+        <v>46098</v>
       </c>
       <c r="C331" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -5868,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C332" s="6">
         <v>1</v>
@@ -5879,7 +5880,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5890,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5901,7 +5902,7 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46031</v>
+        <v>46244</v>
       </c>
       <c r="C335" s="9">
         <v>1</v>
@@ -5912,9 +5913,31 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C336" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B337" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C337" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B338" s="5">
         <v>46155</v>
       </c>
-      <c r="C336" s="6">
+      <c r="C338" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6171,7 +6194,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6369,7 +6392,7 @@
         <v>11</v>
       </c>
       <c r="C26">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -6386,7 +6409,7 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -6494,7 +6517,7 @@
         <v>7</v>
       </c>
       <c r="E33">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6622,7 +6645,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6985,7 +7008,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -7051,7 +7074,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C40">
         <v>11</v>
@@ -7282,7 +7305,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7579,7 +7602,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7920,7 +7943,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -8041,7 +8064,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -8052,7 +8075,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8074,7 +8097,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -8085,7 +8108,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8096,7 +8119,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -8129,7 +8152,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -8140,7 +8163,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8151,7 +8174,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8173,7 +8196,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8184,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -8217,7 +8240,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8239,7 +8262,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8250,7 +8273,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8261,7 +8284,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8272,7 +8295,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8283,7 +8306,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8294,7 +8317,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8305,7 +8328,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8316,7 +8339,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8327,7 +8350,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8360,7 +8383,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8371,7 +8394,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8382,7 +8405,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8393,7 +8416,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8404,7 +8427,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8415,7 +8438,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8426,7 +8449,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8437,7 +8460,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8459,7 +8482,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8470,7 +8493,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8481,7 +8504,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8492,7 +8515,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8503,7 +8526,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8514,7 +8537,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8525,7 +8548,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8536,7 +8559,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>235</v>
+        <v>147</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8547,7 +8570,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8558,7 +8581,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8569,7 +8592,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8591,7 +8614,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8613,7 +8636,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8624,7 +8647,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8635,7 +8658,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8646,7 +8669,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8657,7 +8680,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -8665,13 +8688,13 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C187">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8679,10 +8702,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C188">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8690,10 +8713,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C189">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8701,7 +8724,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="C190">
         <v>16</v>
@@ -8712,10 +8735,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="C191">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -8723,10 +8746,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="C192">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8734,10 +8757,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C193">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8745,10 +8768,10 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C194">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -8756,10 +8779,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="C195">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8767,7 +8790,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C196">
         <v>11</v>
@@ -8778,10 +8801,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C197">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -8800,10 +8823,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C199">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8811,7 +8834,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="C200">
         <v>9</v>
@@ -8822,7 +8845,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="C201">
         <v>9</v>
@@ -8833,10 +8856,10 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C202">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -8844,10 +8867,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="C203">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8855,7 +8878,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="C204">
         <v>7</v>
@@ -8866,7 +8889,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C205">
         <v>7</v>
@@ -8877,10 +8900,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="C206">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -8888,10 +8911,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C207">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8910,7 +8933,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8932,10 +8955,10 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C211">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -8943,7 +8966,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8965,7 +8988,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -8976,7 +8999,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -8987,10 +9010,10 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C216">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -8998,7 +9021,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -9009,7 +9032,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -9020,7 +9043,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -9031,7 +9054,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -9042,7 +9065,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -9053,7 +9076,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -9064,7 +9087,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9075,7 +9098,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -9086,7 +9109,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>194</v>
+        <v>285</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -9097,10 +9120,10 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>286</v>
+        <v>199</v>
       </c>
       <c r="C226">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -9130,7 +9153,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9141,7 +9164,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9152,7 +9175,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9163,7 +9186,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -9174,10 +9197,10 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -9185,7 +9208,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -9196,7 +9219,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9207,7 +9230,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9218,7 +9241,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9229,7 +9252,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9240,7 +9263,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9251,7 +9274,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9262,7 +9285,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9273,7 +9296,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9284,7 +9307,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9295,7 +9318,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9306,7 +9329,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9317,7 +9340,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9328,7 +9351,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9339,7 +9362,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9350,7 +9373,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9361,7 +9384,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9372,7 +9395,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9383,7 +9406,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>225</v>
+        <v>69</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9394,7 +9417,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9405,7 +9428,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9416,7 +9439,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9427,7 +9450,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9438,7 +9461,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9449,7 +9472,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9460,7 +9483,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9482,7 +9505,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9493,7 +9516,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9515,7 +9538,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9526,7 +9549,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9537,7 +9560,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9548,7 +9571,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9559,7 +9582,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9570,7 +9593,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9581,7 +9604,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9592,7 +9615,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9603,7 +9626,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9614,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9647,7 +9670,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C276">
         <v>10</v>
@@ -9669,7 +9692,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C278">
         <v>8</v>
@@ -9680,7 +9703,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C279">
         <v>6</v>
@@ -9702,7 +9725,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -9713,7 +9736,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9735,7 +9758,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9757,7 +9780,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -9768,7 +9791,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -9801,7 +9824,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9812,7 +9835,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9823,7 +9846,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9845,7 +9868,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9922,7 +9945,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9933,7 +9956,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9944,7 +9967,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9966,7 +9989,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9977,7 +10000,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9999,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -10021,7 +10044,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -10032,7 +10055,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -10065,7 +10088,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -10076,7 +10099,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -10087,7 +10110,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -10109,7 +10132,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10120,7 +10143,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10131,7 +10154,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10142,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10164,7 +10187,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10175,7 +10198,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10186,7 +10209,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10197,7 +10220,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10208,7 +10231,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10219,7 +10242,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10230,7 +10253,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10241,7 +10264,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10252,7 +10275,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10263,7 +10286,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10285,7 +10308,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10296,7 +10319,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10329,7 +10352,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10340,7 +10363,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10362,7 +10385,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10373,7 +10396,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10384,7 +10407,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10395,7 +10418,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10428,7 +10451,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10439,7 +10462,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10450,7 +10473,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10461,7 +10484,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -10538,7 +10561,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10549,7 +10572,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10582,7 +10605,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10629,10 +10652,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" t="s">
         <v>270</v>
-      </c>
-      <c r="C1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10640,7 +10663,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>66</v>
@@ -10651,7 +10674,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C3">
         <v>512</v>
@@ -10662,7 +10685,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -10673,7 +10696,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C5">
         <v>13</v>
@@ -10684,7 +10707,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -10695,7 +10718,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -10706,7 +10729,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -10717,10 +10740,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C9">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10728,7 +10751,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10">
         <v>27</v>
@@ -10739,7 +10762,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11">
         <v>29</v>
@@ -10750,7 +10773,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C12">
         <v>28</v>
@@ -10761,7 +10784,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -10772,10 +10795,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10783,7 +10806,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -10794,7 +10817,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -10805,7 +10828,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C17">
         <v>25</v>
@@ -10816,10 +10839,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C18">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -10827,7 +10850,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -10838,7 +10861,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -10849,7 +10872,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -10860,7 +10883,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -10871,7 +10894,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -10882,7 +10905,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C24">
         <v>40</v>
@@ -10893,7 +10916,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C25">
         <v>864</v>
@@ -10904,7 +10927,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -10915,7 +10938,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C27">
         <v>115</v>
@@ -10926,7 +10949,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C28">
         <v>140</v>
@@ -10937,10 +10960,10 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C29">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -10948,7 +10971,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -10959,7 +10982,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10970,7 +10993,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -10981,7 +11004,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10992,7 +11015,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C34">
         <v>704</v>
@@ -11003,7 +11026,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -11014,7 +11037,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C36">
         <v>22</v>
@@ -11025,7 +11048,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C37">
         <v>62</v>
@@ -11036,7 +11059,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C38">
         <v>58</v>
@@ -11047,7 +11070,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C39">
         <v>25</v>
@@ -11058,7 +11081,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -11069,7 +11092,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -11080,7 +11103,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -11091,7 +11114,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -11123,7 +11146,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11230,7 +11253,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -11340,7 +11363,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -11450,7 +11473,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>
